--- a/data/pack/uk/corderos_ni.xlsx
+++ b/data/pack/uk/corderos_ni.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10774,6 +10774,61 @@
         </is>
       </c>
       <c r="K188" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>corderos_ni</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Corderos, en canal (Irlanda del Norte)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6.5978</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>DAERA (Northern Ireland) — Agricultural Market Report</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
         </is>
@@ -10877,7 +10932,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10943,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9">

--- a/data/pack/uk/corderos_ni.xlsx
+++ b/data/pack/uk/corderos_ni.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10829,6 +10829,61 @@
         </is>
       </c>
       <c r="K189" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>corderos_ni</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Corderos, en canal (Irlanda del Norte)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6.5544</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>DAERA (Northern Ireland) — Agricultural Market Report</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
         </is>
@@ -10932,7 +10987,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10998,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
@@ -11038,7 +11093,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
